--- a/Treinamento/erro/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/erro/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\erro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{3EF84936-74B6-48F6-AD3F-F32DF00660B5}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D56601-3E8C-4B53-90AA-1EF4267A0803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
+    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>Processado</t>
-  </si>
-  <si>
-    <t>Alerta: Arquivo  não encontrado para indexação</t>
   </si>
   <si>
     <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; BLOQUEIOS HONDA 28.11.2025.xlsx.</t>
@@ -163,7 +160,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -277,53 +273,53 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="2" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="3" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="4" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -340,10 +336,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -378,7 +374,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -430,7 +426,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -541,21 +537,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -572,7 +568,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -624,25 +620,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
-    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
-    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -675,12 +671,13 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -699,7 +696,7 @@
         <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -719,7 +716,7 @@
         <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -739,7 +736,7 @@
         <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -759,7 +756,7 @@
         <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -779,7 +776,7 @@
         <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -799,7 +796,7 @@
         <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -819,7 +816,7 @@
         <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -839,7 +836,7 @@
         <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -859,7 +856,7 @@
         <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -879,7 +876,7 @@
         <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -899,7 +896,7 @@
         <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -919,7 +916,7 @@
         <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -939,7 +936,7 @@
         <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -959,10 +956,10 @@
         <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -979,10 +976,10 @@
         <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -999,10 +996,10 @@
         <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -1019,10 +1016,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1039,10 +1036,10 @@
         <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -1059,10 +1056,10 @@
         <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -1079,10 +1076,10 @@
         <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
@@ -1099,10 +1096,10 @@
         <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
@@ -1119,10 +1116,10 @@
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
@@ -1139,10 +1136,10 @@
         <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
@@ -1159,10 +1156,10 @@
         <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -1179,10 +1176,10 @@
         <v>39</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1199,10 +1196,10 @@
         <v>39</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>135621231</v>
       </c>
@@ -1219,10 +1216,10 @@
         <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>135623225</v>
       </c>
@@ -1239,10 +1236,10 @@
         <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>135623181</v>
       </c>
@@ -1259,10 +1256,10 @@
         <v>39</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>135621281</v>
       </c>
@@ -1279,10 +1276,10 @@
         <v>39</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>135621378</v>
       </c>
@@ -1299,10 +1296,10 @@
         <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>135621637</v>
       </c>
@@ -1319,10 +1316,10 @@
         <v>39</v>
       </c>
       <c r="F34" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>135622022</v>
       </c>
@@ -1339,10 +1336,10 @@
         <v>39</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>135621980</v>
       </c>
@@ -1359,10 +1356,10 @@
         <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>135622164</v>
       </c>
@@ -1379,10 +1376,10 @@
         <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>135622605</v>
       </c>
@@ -1399,10 +1396,10 @@
         <v>39</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>135622691</v>
       </c>
@@ -1419,48 +1416,48 @@
         <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>